--- a/Excel/EquipSuitConfig.xlsx
+++ b/Excel/EquipSuitConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665E7048-1E64-4A49-9888-058807358FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589C00A0-8AE7-47B7-A80F-DEE940E3ED46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipSuitProto" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -50,7 +50,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -86,7 +86,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="174">
   <si>
     <t>Id</t>
   </si>
@@ -547,6 +547,110 @@
   </si>
   <si>
     <t>15806001,15810001,15810002,15810101,15810102,15810201</t>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xunying Set</t>
+  </si>
+  <si>
+    <t>Spirit Pattern Set</t>
+  </si>
+  <si>
+    <t>War Spirit set</t>
+  </si>
+  <si>
+    <t>Dragon Roar Set</t>
+  </si>
+  <si>
+    <t>Sage Set</t>
+  </si>
+  <si>
+    <t>Fearful Set</t>
+  </si>
+  <si>
+    <t>Heroic Set</t>
+  </si>
+  <si>
+    <t>Longjie Set</t>
+  </si>
+  <si>
+    <t>Magic Spirit Set</t>
+  </si>
+  <si>
+    <t>Order Set</t>
+  </si>
+  <si>
+    <t>Constant Will Set</t>
+  </si>
+  <si>
+    <t>Silver Moon Set</t>
+  </si>
+  <si>
+    <t>Storm Set</t>
+  </si>
+  <si>
+    <t>Infinity Set</t>
+  </si>
+  <si>
+    <t>Inspiration Set</t>
+  </si>
+  <si>
+    <t>Fate Set</t>
+  </si>
+  <si>
+    <t>Holy Spirit Set</t>
+  </si>
+  <si>
+    <t>Dispel Set</t>
+  </si>
+  <si>
+    <t>Destroyer Set</t>
+  </si>
+  <si>
+    <t>Wind Spirit Set</t>
+  </si>
+  <si>
+    <t>Divine Omen Set</t>
+  </si>
+  <si>
+    <t>Eternal Set</t>
+  </si>
+  <si>
+    <t>Kingdom of Power Set</t>
+  </si>
+  <si>
+    <t>Scorching Energy Set</t>
+  </si>
+  <si>
+    <t>Shadow Illusion Set</t>
+  </si>
+  <si>
+    <t>Sacrificial Set</t>
+  </si>
+  <si>
+    <t>Chaos Set</t>
+  </si>
+  <si>
+    <t>Support set</t>
+  </si>
+  <si>
+    <t>Zodiac Set</t>
+  </si>
+  <si>
+    <t>Lu Bu set</t>
+  </si>
+  <si>
+    <t>Si Ma Set</t>
+  </si>
+  <si>
+    <t>Hunter outfit</t>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1604,7 +1708,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1650,6 +1754,7 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="154">
     <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2107,23 +2212,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:L58"/>
+  <dimension ref="C1:M58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="9.125" customWidth="1"/>
     <col min="3" max="3" width="8.5" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="68.875" customWidth="1"/>
-    <col min="6" max="6" width="28.5" customWidth="1"/>
-    <col min="7" max="7" width="28.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="20.625" style="4" customWidth="1"/>
+    <col min="4" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="68.875" customWidth="1"/>
+    <col min="7" max="7" width="28.5" customWidth="1"/>
+    <col min="8" max="8" width="28.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="20.625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="G1" s="5"/>
-      <c r="H1" s="6"/>
-    </row>
-    <row r="3" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
+      <c r="H1" s="5"/>
+      <c r="I1" s="6"/>
+    </row>
+    <row r="2" spans="3:9" x14ac:dyDescent="0.15">
+      <c r="E2" s="17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
@@ -2131,19 +2241,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
@@ -2151,19 +2264,22 @@
         <v>6</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="3:8" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
@@ -2171,885 +2287,999 @@
         <v>12</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>11</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I5" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="9">
         <v>11011</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H6" s="9"/>
+    </row>
+    <row r="7" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="9">
         <v>11012</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="G7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="11"/>
-    </row>
-    <row r="8" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="9">
         <v>11021</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H8" s="9"/>
+    </row>
+    <row r="9" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="9">
         <v>11022</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="G9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="11"/>
-    </row>
-    <row r="10" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="9">
         <v>11031</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H10" s="9"/>
+    </row>
+    <row r="11" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="9">
         <v>11032</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="G11" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="9">
         <v>11041</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="9"/>
-    </row>
-    <row r="13" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H12" s="9"/>
+    </row>
+    <row r="13" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="9">
         <v>11042</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="9"/>
-    </row>
-    <row r="14" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H13" s="9"/>
+    </row>
+    <row r="14" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="9">
         <v>11043</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="9"/>
-    </row>
-    <row r="15" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H14" s="9"/>
+    </row>
+    <row r="15" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="9">
         <v>11051</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="G15" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="11"/>
-    </row>
-    <row r="16" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="9">
         <v>12011</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="G16" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H16" s="9"/>
+    </row>
+    <row r="17" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="9">
         <v>12021</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="9"/>
-    </row>
-    <row r="18" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="9">
         <v>12031</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="9">
         <v>12051</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="G19" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="11"/>
-    </row>
-    <row r="20" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="9">
         <v>13011</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="G20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="9"/>
-    </row>
-    <row r="21" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="9">
         <v>13021</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F21" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="9"/>
-    </row>
-    <row r="22" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="9">
         <v>13031</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="G22" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H22" s="9"/>
+    </row>
+    <row r="23" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="9">
         <v>13051</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F23" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="G23" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G23" s="11"/>
-    </row>
-    <row r="24" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H23" s="11"/>
+    </row>
+    <row r="24" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="9">
         <v>14011</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="G24" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H24" s="9"/>
+    </row>
+    <row r="25" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="9">
         <v>14021</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="G25" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G25" s="9"/>
-    </row>
-    <row r="26" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="9">
         <v>14031</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F26" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="G26" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G26" s="9"/>
-    </row>
-    <row r="27" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H26" s="9"/>
+    </row>
+    <row r="27" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="9">
         <v>14051</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="G27" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G27" s="11"/>
-    </row>
-    <row r="28" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="9">
         <v>15011</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="G28" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G28" s="9"/>
-      <c r="J28" s="14">
-        <v>16000101</v>
-      </c>
-      <c r="K28" s="14">
-        <v>16000105</v>
-      </c>
-      <c r="L28" s="14">
-        <v>16000109</v>
-      </c>
-    </row>
-    <row r="29" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H28" s="9"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+    </row>
+    <row r="29" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="9">
         <v>15021</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F29" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="G29" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="G29" s="9"/>
-      <c r="J29" s="14">
-        <v>16000102</v>
-      </c>
-      <c r="K29" s="14">
-        <v>16000106</v>
-      </c>
-      <c r="L29" s="14">
-        <v>16000110</v>
-      </c>
-    </row>
-    <row r="30" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H29" s="9"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+    </row>
+    <row r="30" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="9">
         <v>15031</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F30" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="G30" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G30" s="9"/>
-      <c r="J30" s="14">
-        <v>16000103</v>
-      </c>
-      <c r="K30" s="14">
-        <v>16000107</v>
-      </c>
-      <c r="L30" s="14">
-        <v>16000111</v>
-      </c>
-    </row>
-    <row r="31" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H30" s="9"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+    </row>
+    <row r="31" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="9">
         <v>15051</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="G31" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G31" s="11"/>
-      <c r="J31" s="14">
-        <v>16000104</v>
-      </c>
-      <c r="K31" s="14">
-        <v>16000108</v>
-      </c>
-      <c r="L31" s="14">
-        <v>16000112</v>
-      </c>
-    </row>
-    <row r="32" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H31" s="11"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+    </row>
+    <row r="32" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="9">
         <v>16011</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F32" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="G32" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H32" s="9"/>
+    </row>
+    <row r="33" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="9">
         <v>16021</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="G33" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="G33" s="9"/>
-      <c r="J33" t="str">
-        <f t="shared" ref="J33:L33" si="0">J28&amp;";"&amp;J29&amp;";"&amp;J30&amp;";"&amp;J31</f>
-        <v>16000101;16000102;16000103;16000104</v>
-      </c>
-      <c r="K33" t="str">
-        <f t="shared" si="0"/>
-        <v>16000105;16000106;16000107;16000108</v>
-      </c>
-      <c r="L33" t="str">
-        <f t="shared" si="0"/>
-        <v>16000109;16000110;16000111;16000112</v>
-      </c>
-    </row>
-    <row r="34" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H33" s="9"/>
+    </row>
+    <row r="34" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="9">
         <v>16031</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F34" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="G34" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="G34" s="9"/>
-    </row>
-    <row r="35" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H34" s="9"/>
+    </row>
+    <row r="35" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="9">
         <v>16051</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F35" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="G35" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="11"/>
-    </row>
-    <row r="36" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H35" s="11"/>
+    </row>
+    <row r="36" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="9">
         <v>17011</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="G36" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="G36" s="9"/>
-    </row>
-    <row r="37" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="9">
         <v>17021</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F37" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="G37" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="G37" s="9"/>
-      <c r="J37" t="str">
-        <f t="shared" ref="J37:L37" si="1">J32&amp;";"&amp;J33&amp;";"&amp;J34&amp;";"&amp;J35</f>
-        <v>;16000101;16000102;16000103;16000104;;</v>
-      </c>
-      <c r="K37" t="str">
-        <f t="shared" si="1"/>
-        <v>;16000105;16000106;16000107;16000108;;</v>
-      </c>
-      <c r="L37" t="str">
-        <f t="shared" si="1"/>
-        <v>;16000109;16000110;16000111;16000112;;</v>
-      </c>
-    </row>
-    <row r="38" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H37" s="9"/>
+    </row>
+    <row r="38" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="9">
         <v>17031</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F38" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="G38" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G38" s="9"/>
-    </row>
-    <row r="39" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H38" s="9"/>
+    </row>
+    <row r="39" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="9">
         <v>17051</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F39" s="15" t="s">
+      <c r="G39" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G39" s="11"/>
-    </row>
-    <row r="40" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H39" s="11"/>
+    </row>
+    <row r="40" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="9">
         <v>18011</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F40" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="G40" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="G40" s="9"/>
-    </row>
-    <row r="41" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H40" s="9"/>
+    </row>
+    <row r="41" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="9">
         <v>18021</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F41" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="G41" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="G41" s="9"/>
-    </row>
-    <row r="42" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H41" s="9"/>
+    </row>
+    <row r="42" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="9">
         <v>18031</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F42" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="G42" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="G42" s="9"/>
-    </row>
-    <row r="43" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H42" s="9"/>
+    </row>
+    <row r="43" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="9">
         <v>18051</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F43" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="F43" s="15" t="s">
+      <c r="G43" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G43" s="11"/>
-    </row>
-    <row r="44" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H43" s="11"/>
+    </row>
+    <row r="44" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="9">
         <v>30001</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="G44" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G44" s="9"/>
-    </row>
-    <row r="45" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H44" s="9"/>
+    </row>
+    <row r="45" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="9">
         <v>30002</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F45" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="G45" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="G45" s="9"/>
-    </row>
-    <row r="46" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H45" s="9"/>
+    </row>
+    <row r="46" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="9">
         <v>30003</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F46" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="G46" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="G46" s="9"/>
-    </row>
-    <row r="47" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H46" s="9"/>
+    </row>
+    <row r="47" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="9">
         <v>30011</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F47" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="G47" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G47" s="9"/>
-    </row>
-    <row r="48" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H47" s="9"/>
+    </row>
+    <row r="48" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="9">
         <v>30012</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="E48" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="G48" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H48" s="9"/>
+    </row>
+    <row r="49" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="9">
         <v>30013</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F49" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="G49" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H49" s="9"/>
+    </row>
+    <row r="50" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="9">
         <v>30021</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F50" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="G50" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G50" s="9"/>
-    </row>
-    <row r="51" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H50" s="9"/>
+    </row>
+    <row r="51" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="9">
         <v>30022</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F51" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="G51" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="G51" s="9"/>
-    </row>
-    <row r="52" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H51" s="9"/>
+    </row>
+    <row r="52" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="9">
         <v>30023</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F52" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="G52" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="G52" s="9"/>
-    </row>
-    <row r="53" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H52" s="9"/>
+    </row>
+    <row r="53" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="9">
         <v>30031</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F53" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="G53" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="G53" s="9"/>
-    </row>
-    <row r="54" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H53" s="9"/>
+    </row>
+    <row r="54" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="9">
         <v>30032</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E54" s="16" t="s">
+      <c r="E54" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F54" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="G54" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="G54" s="9"/>
-    </row>
-    <row r="55" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H54" s="9"/>
+    </row>
+    <row r="55" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="9">
         <v>30033</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E55" s="16" t="s">
+      <c r="E55" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F55" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="G55" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="G55" s="9"/>
-    </row>
-    <row r="56" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H55" s="9"/>
+    </row>
+    <row r="56" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="9">
         <v>40001</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E56" s="16" t="s">
+      <c r="E56" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F56" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="G56" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="G56" s="9">
+      <c r="H56" s="9">
         <v>1</v>
       </c>
-      <c r="H56" s="4">
+      <c r="I56" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="9">
         <v>40002</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E57" s="13">
+      <c r="E57" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F57" s="13">
         <v>10010001</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="G57" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="G57" s="9">
+      <c r="H57" s="9">
         <v>1</v>
       </c>
-      <c r="H57" s="4">
+      <c r="I57" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="9">
         <v>40003</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E58" s="13">
+      <c r="E58" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F58" s="13">
         <v>10010001</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="G58" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="G58" s="9">
+      <c r="H58" s="9">
         <v>1</v>
       </c>
-      <c r="H58" s="4">
+      <c r="I58" s="4">
         <v>3</v>
       </c>
     </row>

--- a/Excel/EquipSuitConfig.xlsx
+++ b/Excel/EquipSuitConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589C00A0-8AE7-47B7-A80F-DEE940E3ED46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7453EC84-62B3-48E9-82CB-BE99684909DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipSuitProto" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="180">
   <si>
     <t>Id</t>
   </si>
@@ -553,103 +553,123 @@
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
-    <t>Xunying Set</t>
-  </si>
-  <si>
-    <t>Spirit Pattern Set</t>
-  </si>
-  <si>
-    <t>War Spirit set</t>
-  </si>
-  <si>
-    <t>Dragon Roar Set</t>
-  </si>
-  <si>
     <t>Sage Set</t>
   </si>
   <si>
-    <t>Fearful Set</t>
-  </si>
-  <si>
-    <t>Heroic Set</t>
-  </si>
-  <si>
-    <t>Longjie Set</t>
-  </si>
-  <si>
-    <t>Magic Spirit Set</t>
-  </si>
-  <si>
     <t>Order Set</t>
   </si>
   <si>
-    <t>Constant Will Set</t>
-  </si>
-  <si>
-    <t>Silver Moon Set</t>
-  </si>
-  <si>
-    <t>Storm Set</t>
-  </si>
-  <si>
-    <t>Infinity Set</t>
-  </si>
-  <si>
-    <t>Inspiration Set</t>
-  </si>
-  <si>
     <t>Fate Set</t>
   </si>
   <si>
     <t>Holy Spirit Set</t>
   </si>
   <si>
-    <t>Dispel Set</t>
-  </si>
-  <si>
     <t>Destroyer Set</t>
   </si>
   <si>
-    <t>Wind Spirit Set</t>
-  </si>
-  <si>
-    <t>Divine Omen Set</t>
-  </si>
-  <si>
     <t>Eternal Set</t>
   </si>
   <si>
-    <t>Kingdom of Power Set</t>
+    <t>Shadow Illusion Set</t>
+  </si>
+  <si>
+    <t>Sacrificial Set</t>
+  </si>
+  <si>
+    <t>Chaos Set</t>
+  </si>
+  <si>
+    <t>Support set</t>
+  </si>
+  <si>
+    <t>Zodiac Set</t>
+  </si>
+  <si>
+    <t>Lu Bu set</t>
+  </si>
+  <si>
+    <t>Si Ma Set</t>
+  </si>
+  <si>
+    <t>Hunter outfit</t>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>Swiftshadow Set</t>
+  </si>
+  <si>
+    <t>Spiritweave Set</t>
+  </si>
+  <si>
+    <t>Warspirit Set</t>
+  </si>
+  <si>
+    <t>Dragonroar Set</t>
+  </si>
+  <si>
+    <t>Daredevil Set</t>
+  </si>
+  <si>
+    <t>Braveheart Set</t>
+  </si>
+  <si>
+    <t>Dragonspine Set</t>
+  </si>
+  <si>
+    <t>Demonspirit Set</t>
+  </si>
+  <si>
+    <t>Endurance Set</t>
+  </si>
+  <si>
+    <t>Silvermoon Set</t>
+  </si>
+  <si>
+    <t>Stormrage Set</t>
+  </si>
+  <si>
+    <t>Endless Set</t>
+  </si>
+  <si>
+    <t>Revelator Set</t>
+  </si>
+  <si>
+    <t>Windspirit Set</t>
+  </si>
+  <si>
+    <t>Oracle Set</t>
+  </si>
+  <si>
+    <t>King's Power Set</t>
+  </si>
+  <si>
+    <t>Phantom Set</t>
+  </si>
+  <si>
+    <t>Priest Set</t>
+  </si>
+  <si>
+    <t>Support Set</t>
+  </si>
+  <si>
+    <t>Lv Bu Set</t>
+  </si>
+  <si>
+    <t>Sima Set</t>
+  </si>
+  <si>
+    <t>Hunter Set</t>
+  </si>
+  <si>
+    <t>Spiritbreaker Set</t>
+    <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
     <t>Scorching Energy Set</t>
-  </si>
-  <si>
-    <t>Shadow Illusion Set</t>
-  </si>
-  <si>
-    <t>Sacrificial Set</t>
-  </si>
-  <si>
-    <t>Chaos Set</t>
-  </si>
-  <si>
-    <t>Support set</t>
-  </si>
-  <si>
-    <t>Zodiac Set</t>
-  </si>
-  <si>
-    <t>Lu Bu set</t>
-  </si>
-  <si>
-    <t>Si Ma Set</t>
-  </si>
-  <si>
-    <t>Hunter outfit</t>
-  </si>
-  <si>
-    <t>Name_EN</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
@@ -2264,7 +2284,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>7</v>
@@ -2310,7 +2330,7 @@
         <v>14</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>15</v>
@@ -2328,7 +2348,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>17</v>
@@ -2346,7 +2366,7 @@
         <v>19</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>20</v>
@@ -2364,7 +2384,7 @@
         <v>19</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>22</v>
@@ -2382,7 +2402,7 @@
         <v>24</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>25</v>
@@ -2400,7 +2420,7 @@
         <v>24</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>27</v>
@@ -2418,7 +2438,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>30</v>
@@ -2436,7 +2456,7 @@
         <v>32</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>33</v>
@@ -2454,7 +2474,7 @@
         <v>35</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>36</v>
@@ -2472,7 +2492,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>39</v>
@@ -2490,7 +2510,7 @@
         <v>41</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>42</v>
@@ -2508,7 +2528,7 @@
         <v>44</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>45</v>
@@ -2526,7 +2546,7 @@
         <v>47</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>48</v>
@@ -2544,7 +2564,7 @@
         <v>50</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>51</v>
@@ -2562,7 +2582,7 @@
         <v>52</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>53</v>
@@ -2580,7 +2600,7 @@
         <v>55</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>56</v>
@@ -2598,7 +2618,7 @@
         <v>58</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>59</v>
@@ -2616,7 +2636,7 @@
         <v>61</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>62</v>
@@ -2634,7 +2654,7 @@
         <v>63</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>64</v>
@@ -2652,7 +2672,7 @@
         <v>66</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>67</v>
@@ -2670,7 +2690,7 @@
         <v>69</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>70</v>
@@ -2688,7 +2708,7 @@
         <v>72</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>73</v>
@@ -2706,7 +2726,7 @@
         <v>74</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>75</v>
@@ -2727,7 +2747,7 @@
         <v>77</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>78</v>
@@ -2748,7 +2768,7 @@
         <v>80</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>81</v>
@@ -2769,7 +2789,7 @@
         <v>83</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>84</v>
@@ -2790,7 +2810,7 @@
         <v>74</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>85</v>
@@ -2808,7 +2828,7 @@
         <v>77</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>87</v>
@@ -2826,7 +2846,7 @@
         <v>80</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>89</v>
@@ -2844,7 +2864,7 @@
         <v>91</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>92</v>
@@ -2862,7 +2882,7 @@
         <v>93</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>94</v>
@@ -2880,7 +2900,7 @@
         <v>96</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>97</v>
@@ -2898,7 +2918,7 @@
         <v>99</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>100</v>
@@ -2916,7 +2936,7 @@
         <v>102</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>103</v>
@@ -2934,7 +2954,7 @@
         <v>93</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="F40" s="16" t="s">
         <v>136</v>
@@ -2952,7 +2972,7 @@
         <v>96</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="F41" s="16" t="s">
         <v>137</v>
@@ -2970,7 +2990,7 @@
         <v>99</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="F42" s="16" t="s">
         <v>138</v>
@@ -2988,7 +3008,7 @@
         <v>102</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="F43" s="16" t="s">
         <v>139</v>
@@ -3006,7 +3026,7 @@
         <v>104</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F44" s="10" t="s">
         <v>105</v>
@@ -3024,7 +3044,7 @@
         <v>104</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>107</v>
@@ -3042,7 +3062,7 @@
         <v>104</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F46" s="10" t="s">
         <v>109</v>
@@ -3060,7 +3080,7 @@
         <v>104</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>111</v>
@@ -3078,7 +3098,7 @@
         <v>104</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>113</v>
@@ -3096,7 +3116,7 @@
         <v>104</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>115</v>
@@ -3114,7 +3134,7 @@
         <v>104</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>117</v>
@@ -3132,7 +3152,7 @@
         <v>104</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>119</v>
@@ -3150,7 +3170,7 @@
         <v>104</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>121</v>
@@ -3168,7 +3188,7 @@
         <v>104</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F53" s="16" t="s">
         <v>123</v>
@@ -3186,7 +3206,7 @@
         <v>104</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F54" s="16" t="s">
         <v>125</v>
@@ -3204,7 +3224,7 @@
         <v>104</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F55" s="16" t="s">
         <v>127</v>
@@ -3222,7 +3242,7 @@
         <v>129</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F56" s="16" t="s">
         <v>130</v>
@@ -3245,7 +3265,7 @@
         <v>131</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="F57" s="13">
         <v>10010001</v>
@@ -3268,7 +3288,7 @@
         <v>132</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="F58" s="13">
         <v>10010001</v>
@@ -3286,7 +3306,7 @@
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/EquipSuitConfig.xlsx
+++ b/Excel/EquipSuitConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7453EC84-62B3-48E9-82CB-BE99684909DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3F7B12-BCEF-4D12-A5A4-0033048B0342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="195">
   <si>
     <t>Id</t>
   </si>
@@ -670,6 +670,59 @@
   </si>
   <si>
     <t>Scorching Energy Set</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>15901001,15902001,15903001,15904001,15905001,15911001</t>
+  </si>
+  <si>
+    <t>15901002,15902002,15903002,15904002,15905002,15911002</t>
+  </si>
+  <si>
+    <t>15901003,15902003,15903003,15904003,15905003,15911003</t>
+  </si>
+  <si>
+    <t>15906001,15910001,15910002,15910101,15910102,15910201</t>
+  </si>
+  <si>
+    <t>2,190111;4,190112;6,190113</t>
+  </si>
+  <si>
+    <t>2,190121;4,190122;6,190123</t>
+  </si>
+  <si>
+    <t>2,190131;4,190132;6,190133</t>
+  </si>
+  <si>
+    <t>光翼套装</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>天云套装</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>神御套装</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>极天套装</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>破晓套装</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣辉套装</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>耀世套装</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>万象套装</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
@@ -882,7 +935,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -910,12 +963,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14889980773339029"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14954069643238624"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1286,13 +1333,13 @@
   </borders>
   <cellStyleXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -1301,13 +1348,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
@@ -1320,295 +1367,295 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1618,7 +1665,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
@@ -1670,7 +1717,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1682,16 +1729,19 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1700,35 +1750,32 @@
     <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="40" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="39" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1763,9 +1810,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2232,7 +2276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:M58"/>
+  <dimension ref="C1:I62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="9.125" customWidth="1"/>
@@ -2249,7 +2293,7 @@
       <c r="I1" s="6"/>
     </row>
     <row r="2" spans="3:9" x14ac:dyDescent="0.15">
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2353,7 +2397,7 @@
       <c r="F7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>18</v>
       </c>
       <c r="H7" s="11"/>
@@ -2389,7 +2433,7 @@
       <c r="F9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="11"/>
@@ -2425,7 +2469,7 @@
       <c r="F11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>28</v>
       </c>
       <c r="H11" s="11"/>
@@ -2497,7 +2541,7 @@
       <c r="F15" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="14" t="s">
         <v>40</v>
       </c>
       <c r="H15" s="11"/>
@@ -2520,7 +2564,7 @@
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="9">
         <v>12021</v>
       </c>
@@ -2538,7 +2582,7 @@
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="9">
         <v>12031</v>
       </c>
@@ -2556,7 +2600,7 @@
       </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="9">
         <v>12051</v>
       </c>
@@ -2569,12 +2613,12 @@
       <c r="F19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="14" t="s">
         <v>40</v>
       </c>
       <c r="H19" s="11"/>
     </row>
-    <row r="20" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="9">
         <v>13011</v>
       </c>
@@ -2592,7 +2636,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="9">
         <v>13021</v>
       </c>
@@ -2610,7 +2654,7 @@
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="9">
         <v>13031</v>
       </c>
@@ -2628,7 +2672,7 @@
       </c>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="9">
         <v>13051</v>
       </c>
@@ -2641,12 +2685,12 @@
       <c r="F23" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>40</v>
       </c>
       <c r="H23" s="11"/>
     </row>
-    <row r="24" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="9">
         <v>14011</v>
       </c>
@@ -2664,7 +2708,7 @@
       </c>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="9">
         <v>14021</v>
       </c>
@@ -2682,7 +2726,7 @@
       </c>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="9">
         <v>14031</v>
       </c>
@@ -2700,7 +2744,7 @@
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="9">
         <v>14051</v>
       </c>
@@ -2713,12 +2757,12 @@
       <c r="F27" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="G27" s="14" t="s">
         <v>40</v>
       </c>
       <c r="H27" s="11"/>
     </row>
-    <row r="28" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="9">
         <v>15011</v>
       </c>
@@ -2735,11 +2779,8 @@
         <v>76</v>
       </c>
       <c r="H28" s="9"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-    </row>
-    <row r="29" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="29" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="9">
         <v>15021</v>
       </c>
@@ -2756,11 +2797,8 @@
         <v>79</v>
       </c>
       <c r="H29" s="9"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-    </row>
-    <row r="30" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="30" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="9">
         <v>15031</v>
       </c>
@@ -2777,11 +2815,8 @@
         <v>82</v>
       </c>
       <c r="H30" s="9"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-    </row>
-    <row r="31" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="31" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="9">
         <v>15051</v>
       </c>
@@ -2794,15 +2829,12 @@
       <c r="F31" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="14" t="s">
         <v>40</v>
       </c>
       <c r="H31" s="11"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-    </row>
-    <row r="32" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="32" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="9">
         <v>16011</v>
       </c>
@@ -2869,7 +2901,7 @@
       <c r="F35" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" s="14" t="s">
         <v>40</v>
       </c>
       <c r="H35" s="11"/>
@@ -2941,7 +2973,7 @@
       <c r="F39" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="G39" s="15" t="s">
+      <c r="G39" s="14" t="s">
         <v>40</v>
       </c>
       <c r="H39" s="11"/>
@@ -2951,12 +2983,12 @@
         <v>18011</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="F40" s="15" t="s">
         <v>136</v>
       </c>
       <c r="G40" s="9" t="s">
@@ -2969,12 +3001,12 @@
         <v>18021</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>96</v>
+        <v>188</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="F41" s="15" t="s">
         <v>137</v>
       </c>
       <c r="G41" s="9" t="s">
@@ -2987,12 +3019,12 @@
         <v>18031</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="15" t="s">
         <v>138</v>
       </c>
       <c r="G42" s="9" t="s">
@@ -3005,94 +3037,94 @@
         <v>18051</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>102</v>
+        <v>190</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="G43" s="14" t="s">
         <v>40</v>
       </c>
       <c r="H43" s="11"/>
     </row>
     <row r="44" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="9">
-        <v>30001</v>
+        <v>19011</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>104</v>
+        <v>191</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>105</v>
+        <v>147</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>180</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="9">
-        <v>30002</v>
+        <v>19021</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>104</v>
+        <v>192</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>107</v>
+        <v>148</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>181</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="H45" s="9"/>
     </row>
     <row r="46" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="9">
-        <v>30003</v>
+        <v>19031</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>109</v>
+        <v>149</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>182</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="H46" s="9"/>
     </row>
     <row r="47" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="9">
-        <v>30011</v>
+        <v>19051</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H47" s="9"/>
+        <v>150</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="H47" s="11"/>
     </row>
     <row r="48" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="9">
-        <v>30012</v>
+        <v>30001</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>104</v>
@@ -3101,16 +3133,16 @@
         <v>151</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="9">
-        <v>30013</v>
+        <v>30002</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>104</v>
@@ -3119,16 +3151,16 @@
         <v>151</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H49" s="9"/>
     </row>
     <row r="50" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="9">
-        <v>30021</v>
+        <v>30003</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>104</v>
@@ -3137,16 +3169,16 @@
         <v>151</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H50" s="9"/>
     </row>
     <row r="51" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="9">
-        <v>30022</v>
+        <v>30011</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>104</v>
@@ -3155,16 +3187,16 @@
         <v>151</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="H51" s="9"/>
     </row>
     <row r="52" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="9">
-        <v>30023</v>
+        <v>30012</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>104</v>
@@ -3173,16 +3205,16 @@
         <v>151</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H52" s="9"/>
     </row>
     <row r="53" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="9">
-        <v>30031</v>
+        <v>30013</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>104</v>
@@ -3190,17 +3222,17 @@
       <c r="E53" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F53" s="16" t="s">
-        <v>123</v>
+      <c r="F53" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H53" s="9"/>
     </row>
     <row r="54" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="9">
-        <v>30032</v>
+        <v>30021</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>104</v>
@@ -3208,17 +3240,17 @@
       <c r="E54" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F54" s="16" t="s">
-        <v>125</v>
+      <c r="F54" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H54" s="9"/>
     </row>
     <row r="55" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="9">
-        <v>30033</v>
+        <v>30022</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>104</v>
@@ -3226,80 +3258,152 @@
       <c r="E55" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F55" s="16" t="s">
-        <v>127</v>
+      <c r="F55" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="H55" s="9"/>
     </row>
     <row r="56" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="9">
-        <v>40001</v>
+        <v>30023</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F56" s="16" t="s">
-        <v>130</v>
+        <v>151</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="H56" s="9">
-        <v>1</v>
-      </c>
-      <c r="I56" s="4">
-        <v>1</v>
-      </c>
+      <c r="H56" s="9"/>
     </row>
     <row r="57" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="9">
-        <v>40002</v>
+        <v>30031</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F57" s="13">
-        <v>10010001</v>
+        <v>151</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="H57" s="9">
-        <v>1</v>
-      </c>
-      <c r="I57" s="4">
-        <v>2</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="H57" s="9"/>
     </row>
     <row r="58" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="9">
+        <v>30032</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H58" s="9"/>
+    </row>
+    <row r="59" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C59" s="9">
+        <v>30033</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H59" s="9"/>
+    </row>
+    <row r="60" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C60" s="9">
+        <v>40001</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F60" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H60" s="9">
+        <v>1</v>
+      </c>
+      <c r="I60" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C61" s="9">
+        <v>40002</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F61" s="13">
+        <v>10010001</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H61" s="9">
+        <v>1</v>
+      </c>
+      <c r="I61" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C62" s="9">
         <v>40003</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D62" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E62" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F58" s="13">
+      <c r="F62" s="13">
         <v>10010001</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="G62" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H62" s="9">
         <v>1</v>
       </c>
-      <c r="I58" s="4">
+      <c r="I62" s="4">
         <v>3</v>
       </c>
     </row>

--- a/Excel/EquipSuitConfig.xlsx
+++ b/Excel/EquipSuitConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3F7B12-BCEF-4D12-A5A4-0033048B0342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C370FD-1E2F-44CF-B3A8-DFC0BA32AEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3930" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipSuitProto" sheetId="1" r:id="rId1"/>
@@ -282,9 +282,6 @@
     <t>恒心套装</t>
   </si>
   <si>
-    <t>15206003,15210011,15210012,15210111,15210112,15200211</t>
-  </si>
-  <si>
     <t>银月套装</t>
   </si>
   <si>
@@ -723,6 +720,10 @@
   </si>
   <si>
     <t>万象套装</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>15206003,15210011,15210012,15210111,15210112,15210211</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
@@ -2294,7 +2295,7 @@
     </row>
     <row r="2" spans="3:9" x14ac:dyDescent="0.15">
       <c r="E2" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="3:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2328,7 +2329,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>7</v>
@@ -2374,7 +2375,7 @@
         <v>14</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>15</v>
@@ -2392,7 +2393,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>17</v>
@@ -2410,7 +2411,7 @@
         <v>19</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>20</v>
@@ -2428,7 +2429,7 @@
         <v>19</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>22</v>
@@ -2446,7 +2447,7 @@
         <v>24</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>25</v>
@@ -2464,7 +2465,7 @@
         <v>24</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>27</v>
@@ -2482,7 +2483,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>30</v>
@@ -2500,7 +2501,7 @@
         <v>32</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>33</v>
@@ -2518,7 +2519,7 @@
         <v>35</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>36</v>
@@ -2536,7 +2537,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>39</v>
@@ -2554,7 +2555,7 @@
         <v>41</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>42</v>
@@ -2572,7 +2573,7 @@
         <v>44</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>45</v>
@@ -2590,7 +2591,7 @@
         <v>47</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>48</v>
@@ -2608,10 +2609,10 @@
         <v>50</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>40</v>
@@ -2623,16 +2624,16 @@
         <v>13011</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F20" s="10" t="s">
+      <c r="G20" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="H20" s="9"/>
     </row>
@@ -2641,16 +2642,16 @@
         <v>13021</v>
       </c>
       <c r="D21" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="F21" s="10" t="s">
+      <c r="G21" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="H21" s="9"/>
     </row>
@@ -2659,16 +2660,16 @@
         <v>13031</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F22" s="10" t="s">
+      <c r="G22" s="9" t="s">
         <v>59</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>60</v>
       </c>
       <c r="H22" s="9"/>
     </row>
@@ -2677,13 +2678,13 @@
         <v>13051</v>
       </c>
       <c r="D23" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F23" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="G23" s="14" t="s">
         <v>40</v>
@@ -2695,16 +2696,16 @@
         <v>14011</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F24" s="10" t="s">
+      <c r="G24" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>65</v>
       </c>
       <c r="H24" s="9"/>
     </row>
@@ -2713,16 +2714,16 @@
         <v>14021</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F25" s="10" t="s">
+      <c r="G25" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>68</v>
       </c>
       <c r="H25" s="9"/>
     </row>
@@ -2731,16 +2732,16 @@
         <v>14031</v>
       </c>
       <c r="D26" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F26" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F26" s="10" t="s">
+      <c r="G26" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -2749,13 +2750,13 @@
         <v>14051</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>72</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>40</v>
@@ -2767,16 +2768,16 @@
         <v>15011</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F28" s="10" t="s">
+      <c r="G28" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -2785,16 +2786,16 @@
         <v>15021</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F29" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F29" s="10" t="s">
+      <c r="G29" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>79</v>
       </c>
       <c r="H29" s="9"/>
     </row>
@@ -2803,16 +2804,16 @@
         <v>15031</v>
       </c>
       <c r="D30" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F30" s="10" t="s">
+      <c r="G30" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>82</v>
       </c>
       <c r="H30" s="9"/>
     </row>
@@ -2821,13 +2822,13 @@
         <v>15051</v>
       </c>
       <c r="D31" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="G31" s="14" t="s">
         <v>40</v>
@@ -2839,16 +2840,16 @@
         <v>16011</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F32" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G32" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="H32" s="9"/>
     </row>
@@ -2857,16 +2858,16 @@
         <v>16021</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F33" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="H33" s="9"/>
     </row>
@@ -2875,16 +2876,16 @@
         <v>16031</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F34" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="H34" s="9"/>
     </row>
@@ -2893,13 +2894,13 @@
         <v>16051</v>
       </c>
       <c r="D35" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>92</v>
       </c>
       <c r="G35" s="14" t="s">
         <v>40</v>
@@ -2911,16 +2912,16 @@
         <v>17011</v>
       </c>
       <c r="D36" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E36" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F36" s="10" t="s">
+      <c r="G36" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="H36" s="9"/>
     </row>
@@ -2929,16 +2930,16 @@
         <v>17021</v>
       </c>
       <c r="D37" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F37" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F37" s="10" t="s">
+      <c r="G37" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>98</v>
       </c>
       <c r="H37" s="9"/>
     </row>
@@ -2947,16 +2948,16 @@
         <v>17031</v>
       </c>
       <c r="D38" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="F38" s="10" t="s">
+      <c r="G38" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="H38" s="9"/>
     </row>
@@ -2965,13 +2966,13 @@
         <v>17051</v>
       </c>
       <c r="D39" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F39" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="G39" s="14" t="s">
         <v>40</v>
@@ -2983,16 +2984,16 @@
         <v>18011</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H40" s="9"/>
     </row>
@@ -3001,16 +3002,16 @@
         <v>18021</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H41" s="9"/>
     </row>
@@ -3019,16 +3020,16 @@
         <v>18031</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H42" s="9"/>
     </row>
@@ -3037,13 +3038,13 @@
         <v>18051</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G43" s="14" t="s">
         <v>40</v>
@@ -3055,16 +3056,16 @@
         <v>19011</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H44" s="9"/>
     </row>
@@ -3073,16 +3074,16 @@
         <v>19021</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H45" s="9"/>
     </row>
@@ -3091,16 +3092,16 @@
         <v>19031</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H46" s="9"/>
     </row>
@@ -3109,13 +3110,13 @@
         <v>19051</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>40</v>
@@ -3127,16 +3128,16 @@
         <v>30001</v>
       </c>
       <c r="D48" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E48" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F48" s="10" t="s">
+      <c r="G48" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="H48" s="9"/>
     </row>
@@ -3145,16 +3146,16 @@
         <v>30002</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F49" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="H49" s="9"/>
     </row>
@@ -3163,16 +3164,16 @@
         <v>30003</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F50" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G50" s="9" t="s">
         <v>109</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>110</v>
       </c>
       <c r="H50" s="9"/>
     </row>
@@ -3181,16 +3182,16 @@
         <v>30011</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F51" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G51" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="H51" s="9"/>
     </row>
@@ -3199,16 +3200,16 @@
         <v>30012</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F52" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G52" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>114</v>
       </c>
       <c r="H52" s="9"/>
     </row>
@@ -3217,16 +3218,16 @@
         <v>30013</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F53" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="H53" s="9"/>
     </row>
@@ -3235,16 +3236,16 @@
         <v>30021</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F54" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="G54" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>118</v>
       </c>
       <c r="H54" s="9"/>
     </row>
@@ -3253,16 +3254,16 @@
         <v>30022</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F55" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>120</v>
       </c>
       <c r="H55" s="9"/>
     </row>
@@ -3271,16 +3272,16 @@
         <v>30023</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F56" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="G56" s="9" t="s">
         <v>121</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>122</v>
       </c>
       <c r="H56" s="9"/>
     </row>
@@ -3289,16 +3290,16 @@
         <v>30031</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F57" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="H57" s="9"/>
     </row>
@@ -3307,16 +3308,16 @@
         <v>30032</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F58" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="G58" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="H58" s="9"/>
     </row>
@@ -3325,16 +3326,16 @@
         <v>30033</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F59" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>127</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="H59" s="9"/>
     </row>
@@ -3343,16 +3344,16 @@
         <v>40001</v>
       </c>
       <c r="D60" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F60" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E60" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>130</v>
-      </c>
       <c r="G60" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H60" s="9">
         <v>1</v>
@@ -3366,16 +3367,16 @@
         <v>40002</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F61" s="13">
         <v>10010001</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H61" s="9">
         <v>1</v>
@@ -3389,16 +3390,16 @@
         <v>40003</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F62" s="13">
         <v>10010001</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H62" s="9">
         <v>1</v>

--- a/Excel/EquipSuitConfig.xlsx
+++ b/Excel/EquipSuitConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C370FD-1E2F-44CF-B3A8-DFC0BA32AEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5FF284-A1B9-439F-8945-DBF89FE8FC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3930" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipSuitProto" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="198">
   <si>
     <t>Id</t>
   </si>
@@ -725,6 +725,15 @@
   <si>
     <t>15206003,15210011,15210012,15210111,15210112,15210211</t>
     <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>16000501,16000502,16000503,16000504</t>
+  </si>
+  <si>
+    <t>16000505,16000506,16000507,16000508</t>
+  </si>
+  <si>
+    <t>16000509,16000510,16000511,16000512</t>
   </si>
 </sst>
 </file>
@@ -2277,7 +2286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:I62"/>
+  <dimension ref="C1:I65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="9.125" customWidth="1"/>
@@ -3341,70 +3350,124 @@
     </row>
     <row r="60" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="9">
-        <v>40001</v>
+        <v>30041</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H60" s="9">
-        <v>1</v>
-      </c>
-      <c r="I60" s="4">
-        <v>1</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H60" s="9"/>
     </row>
     <row r="61" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="9">
-        <v>40002</v>
+        <v>30042</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F61" s="13">
-        <v>10010001</v>
+        <v>150</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>196</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H61" s="9">
-        <v>1</v>
-      </c>
-      <c r="I61" s="4">
-        <v>2</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="H61" s="9"/>
     </row>
     <row r="62" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="9">
+        <v>30043</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H62" s="9"/>
+    </row>
+    <row r="63" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C63" s="9">
+        <v>40001</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H63" s="9">
+        <v>1</v>
+      </c>
+      <c r="I63" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C64" s="9">
+        <v>40002</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F64" s="13">
+        <v>10010001</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H64" s="9">
+        <v>1</v>
+      </c>
+      <c r="I64" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C65" s="9">
         <v>40003</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D65" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E62" s="9" t="s">
+      <c r="E65" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F62" s="13">
+      <c r="F65" s="13">
         <v>10010001</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G65" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="H62" s="9">
+      <c r="H65" s="9">
         <v>1</v>
       </c>
-      <c r="I62" s="4">
+      <c r="I65" s="4">
         <v>3</v>
       </c>
     </row>

--- a/Excel/EquipSuitConfig.xlsx
+++ b/Excel/EquipSuitConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5FF284-A1B9-439F-8945-DBF89FE8FC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48F0669-A7FC-4957-9BD3-C74E23A4057B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="201">
   <si>
     <t>Id</t>
   </si>
@@ -734,6 +734,15 @@
   </si>
   <si>
     <t>16000509,16000510,16000511,16000512</t>
+  </si>
+  <si>
+    <t>2,300411;3,300412;4,300413</t>
+  </si>
+  <si>
+    <t>2,300421;3,300422;4,300423</t>
+  </si>
+  <si>
+    <t>2,300431;3,300432;4,300433</t>
   </si>
 </sst>
 </file>
@@ -3362,7 +3371,7 @@
         <v>195</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="H60" s="9"/>
     </row>
@@ -3380,7 +3389,7 @@
         <v>196</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="H61" s="9"/>
     </row>
@@ -3398,7 +3407,7 @@
         <v>197</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>127</v>
+        <v>200</v>
       </c>
       <c r="H62" s="9"/>
     </row>
